--- a/tests/fixtures/directory_employees_1.xlsx
+++ b/tests/fixtures/directory_employees_1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
   <si>
     <t>Договоры</t>
   </si>
@@ -29,6 +29,24 @@
   </si>
   <si>
     <t>Должность</t>
+  </si>
+  <si>
+    <t>Вид удостоверения личности</t>
+  </si>
+  <si>
+    <t>Серия</t>
+  </si>
+  <si>
+    <t>Номер</t>
+  </si>
+  <si>
+    <t>Дата выдачи</t>
+  </si>
+  <si>
+    <t>Кем выдано</t>
+  </si>
+  <si>
+    <t>Адрес места проживания</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1242,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr defaultColWidth="10.6" defaultRowHeight="11.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
@@ -1235,9 +1253,15 @@
     <col min="8" max="9" width="1.60156" style="1" customWidth="1"/>
     <col min="10" max="10" width="2.8125" style="1" customWidth="1"/>
     <col min="11" max="11" width="8.42188" style="1" customWidth="1"/>
-    <col min="12" max="12" width="33.4219" style="1" customWidth="1"/>
-    <col min="13" max="13" width="35" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="10.6016" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.8125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.2109" style="1" customWidth="1"/>
+    <col min="14" max="14" width="35" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7" style="1" customWidth="1"/>
+    <col min="16" max="16" width="7.21094" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.4219" style="1" customWidth="1"/>
+    <col min="19" max="19" width="24.6016" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="10.6016" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1">
@@ -1254,6 +1278,12 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" t="s" s="3">
@@ -1271,6 +1301,12 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
     </row>
     <row r="3" ht="10" customHeight="1">
       <c r="A3" s="5"/>
@@ -1286,6 +1322,12 @@
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="s" s="6">
@@ -1311,6 +1353,24 @@
       <c r="M4" t="s" s="6">
         <v>5</v>
       </c>
+      <c r="N4" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s" s="6">
+        <v>7</v>
+      </c>
+      <c r="P4" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="s" s="6">
+        <v>9</v>
+      </c>
+      <c r="R4" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="S4" t="s" s="6">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" ht="11" customHeight="1">
       <c r="A5" s="8"/>
@@ -1326,6 +1386,12 @@
       <c r="K5" s="9"/>
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
     </row>
     <row r="6" ht="11" customHeight="1">
       <c r="A6" s="8"/>
@@ -1341,6 +1407,12 @@
       <c r="K6" s="9"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
     </row>
     <row r="7" ht="11" customHeight="1">
       <c r="A7" s="9"/>
@@ -1356,6 +1428,12 @@
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
     </row>
     <row r="8" ht="11" customHeight="1">
       <c r="A8" s="9"/>
@@ -1371,6 +1449,12 @@
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
     </row>
     <row r="9" ht="11" customHeight="1">
       <c r="A9" s="9"/>
@@ -1386,6 +1470,12 @@
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
     </row>
     <row r="10" ht="11" customHeight="1">
       <c r="A10" s="9"/>
@@ -1401,6 +1491,12 @@
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
     </row>
     <row r="11" ht="11" customHeight="1">
       <c r="A11" s="9"/>
@@ -1416,6 +1512,12 @@
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
     </row>
     <row r="12" ht="11" customHeight="1">
       <c r="A12" s="9"/>
@@ -1431,6 +1533,12 @@
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
     </row>
     <row r="13" ht="11" customHeight="1">
       <c r="A13" s="9"/>
@@ -1446,6 +1554,12 @@
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
     </row>
     <row r="14" ht="11" customHeight="1">
       <c r="A14" s="9"/>
@@ -1461,6 +1575,12 @@
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
     </row>
     <row r="15" ht="11" customHeight="1">
       <c r="A15" s="9"/>
@@ -1476,6 +1596,12 @@
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
     </row>
     <row r="16" ht="11" customHeight="1">
       <c r="A16" s="9"/>
@@ -1491,6 +1617,12 @@
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
     </row>
     <row r="17" ht="11" customHeight="1">
       <c r="A17" s="9"/>
@@ -1506,6 +1638,12 @@
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
     </row>
     <row r="18" ht="23" customHeight="1">
       <c r="A18" s="9"/>
@@ -1521,6 +1659,12 @@
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
     </row>
     <row r="19" ht="23" customHeight="1">
       <c r="A19" s="9"/>
@@ -1536,6 +1680,12 @@
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
     </row>
     <row r="20" ht="23" customHeight="1">
       <c r="A20" s="9"/>
@@ -1551,6 +1701,12 @@
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
     </row>
     <row r="21" ht="11" customHeight="1">
       <c r="A21" s="9"/>
@@ -1566,6 +1722,12 @@
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
     </row>
     <row r="22" ht="11" customHeight="1">
       <c r="A22" s="9"/>
@@ -1581,6 +1743,12 @@
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
       <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
     </row>
     <row r="23" ht="11" customHeight="1">
       <c r="A23" s="9"/>
@@ -1596,6 +1764,12 @@
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
     </row>
     <row r="24" ht="11" customHeight="1">
       <c r="A24" s="9"/>
@@ -1611,6 +1785,12 @@
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
     </row>
     <row r="25" ht="11" customHeight="1">
       <c r="A25" s="9"/>
@@ -1626,6 +1806,12 @@
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
     </row>
     <row r="26" ht="11" customHeight="1">
       <c r="A26" s="9"/>
@@ -1641,6 +1827,12 @@
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
     </row>
     <row r="27" ht="11" customHeight="1">
       <c r="A27" s="9"/>
@@ -1656,6 +1848,12 @@
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
     </row>
     <row r="28" ht="11" customHeight="1">
       <c r="A28" s="9"/>
@@ -1671,6 +1869,12 @@
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
     </row>
     <row r="29" ht="23" customHeight="1">
       <c r="A29" s="9"/>
@@ -1686,6 +1890,12 @@
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
     </row>
     <row r="30" ht="11" customHeight="1">
       <c r="A30" s="9"/>
@@ -1701,6 +1911,12 @@
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
     </row>
     <row r="31" ht="11" customHeight="1">
       <c r="A31" s="9"/>
@@ -1716,6 +1932,12 @@
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
       <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
     </row>
     <row r="32" ht="11" customHeight="1">
       <c r="A32" s="9"/>
@@ -1731,6 +1953,12 @@
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
     </row>
     <row r="33" ht="11" customHeight="1">
       <c r="A33" s="9"/>
@@ -1746,6 +1974,12 @@
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
     </row>
     <row r="34" ht="11" customHeight="1">
       <c r="A34" s="9"/>
@@ -1761,6 +1995,12 @@
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9"/>
     </row>
     <row r="35" ht="11" customHeight="1">
       <c r="A35" s="9"/>
@@ -1776,6 +2016,12 @@
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="96">
